--- a/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.3_Requirements_Register_20260301.xlsx
+++ b/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.3_Requirements_Register_20260301.xlsx
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="R3" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="4">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="R4" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="5">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="R5" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="6">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="R6" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="7">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="R7" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="8">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="R8" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="9">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="R9" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="10">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="R10" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="11">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="R11" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="12">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="R12" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="13">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="R13" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
     <row r="14">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="R14" s="15" t="n">
-        <v>46082.50844681912</v>
+        <v>46082.7482215283</v>
       </c>
     </row>
   </sheetData>
